--- a/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Engineering Introduction/What is Data Engineering/What_is_Data_Engineering (1).xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING FOUNDATION/Data Engineering Introduction/What is Data Engineering/What_is_Data_Engineering (1).xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,12 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Answer</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -489,12 +484,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -529,12 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -569,12 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -609,12 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -649,12 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -689,12 +659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -729,12 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -769,12 +729,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -809,12 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -849,12 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -889,12 +834,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -929,12 +869,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -969,12 +904,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1009,12 +939,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1049,12 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1009,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1044,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1079,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1114,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1149,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
